--- a/03_Outputs/all/idx6_crecimiento_loadings_y_tops.xlsx
+++ b/03_Outputs/all/idx6_crecimiento_loadings_y_tops.xlsx
@@ -396,10 +396,10 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.2213110964443284</v>
+        <v>0.2213110964443281</v>
       </c>
       <c r="D2">
-        <v>0.08485281400535553</v>
+        <v>0.08485281400535535</v>
       </c>
       <c r="E2">
         <v>8.5</v>
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="C3">
-        <v>-0.05178304128717547</v>
+        <v>-0.05178304128717581</v>
       </c>
       <c r="D3">
-        <v>0.01985411866628954</v>
+        <v>0.01985411866628966</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -438,10 +438,10 @@
         </is>
       </c>
       <c r="C4">
-        <v>0.1148517480293739</v>
+        <v>0.1148517480293745</v>
       </c>
       <c r="D4">
-        <v>0.04403527057748746</v>
+        <v>0.04403527057748766</v>
       </c>
       <c r="E4">
         <v>4.4</v>
@@ -459,10 +459,10 @@
         </is>
       </c>
       <c r="C5">
-        <v>0.3254249083447185</v>
+        <v>0.3254249083447182</v>
       </c>
       <c r="D5">
-        <v>0.1247710560569676</v>
+        <v>0.1247710560569674</v>
       </c>
       <c r="E5">
         <v>12.5</v>
@@ -480,10 +480,10 @@
         </is>
       </c>
       <c r="C6">
-        <v>0.2600068618528435</v>
+        <v>0.2600068618528437</v>
       </c>
       <c r="D6">
-        <v>0.09968914457240217</v>
+        <v>0.0996891445724022</v>
       </c>
       <c r="E6">
         <v>10</v>
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="C7">
-        <v>0.5003681093865645</v>
+        <v>0.5003681093865647</v>
       </c>
       <c r="D7">
-        <v>0.1918459706816821</v>
+        <v>0.191845970681682</v>
       </c>
       <c r="E7">
         <v>19.2</v>
@@ -522,10 +522,10 @@
         </is>
       </c>
       <c r="C8">
-        <v>0.5904655784019618</v>
+        <v>0.5904655784019622</v>
       </c>
       <c r="D8">
-        <v>0.2263902113616333</v>
+        <v>0.2263902113616334</v>
       </c>
       <c r="E8">
         <v>22.6</v>
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="C9">
-        <v>0.1863165917715679</v>
+        <v>0.1863165917715682</v>
       </c>
       <c r="D9">
-        <v>0.07143558258806754</v>
+        <v>0.07143558258806761</v>
       </c>
       <c r="E9">
         <v>7.1</v>
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="C10">
-        <v>0.357648340525302</v>
+        <v>0.3576483405253019</v>
       </c>
       <c r="D10">
-        <v>0.1371258314901147</v>
+        <v>0.1371258314901146</v>
       </c>
       <c r="E10">
         <v>13.7</v>
@@ -588,7 +588,7 @@
         <v>0.5304316923610908</v>
       </c>
       <c r="D11">
-        <v>0.2038855610100351</v>
+        <v>0.2038855610100354</v>
       </c>
       <c r="E11">
         <v>20.4</v>
@@ -606,10 +606,10 @@
         </is>
       </c>
       <c r="C12">
-        <v>0.007763770756149372</v>
+        <v>0.007763770756148314</v>
       </c>
       <c r="D12">
-        <v>0.002984212253843324</v>
+        <v>0.002984212253842921</v>
       </c>
       <c r="E12">
         <v>0.3</v>
@@ -627,10 +627,10 @@
         </is>
       </c>
       <c r="C13">
-        <v>-0.1238794609034083</v>
+        <v>-0.1238794609034084</v>
       </c>
       <c r="D13">
-        <v>0.04761637313088429</v>
+        <v>0.04761637313088438</v>
       </c>
       <c r="E13">
         <v>4.8</v>
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="C14">
-        <v>0.3830548014776221</v>
+        <v>0.3830548014776216</v>
       </c>
       <c r="D14">
         <v>0.1472373242805533</v>
@@ -669,10 +669,10 @@
         </is>
       </c>
       <c r="C15">
-        <v>-0.3648822813276321</v>
+        <v>-0.3648822813276324</v>
       </c>
       <c r="D15">
-        <v>0.1402522317246119</v>
+        <v>0.1402522317246122</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="C16">
-        <v>-0.3235297503896482</v>
+        <v>-0.3235297503896475</v>
       </c>
       <c r="D16">
-        <v>0.1243572840981866</v>
+        <v>0.1243572840981864</v>
       </c>
       <c r="E16">
         <v>12.4</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="C17">
-        <v>-0.200961388186444</v>
+        <v>-0.2009613881864435</v>
       </c>
       <c r="D17">
-        <v>0.07724486670350791</v>
+        <v>0.07724486670350783</v>
       </c>
       <c r="E17">
         <v>7.7</v>
@@ -732,10 +732,10 @@
         </is>
       </c>
       <c r="C18">
-        <v>-0.1665381529164315</v>
+        <v>-0.1665381529164311</v>
       </c>
       <c r="D18">
-        <v>0.06401337858565775</v>
+        <v>0.06401337858565767</v>
       </c>
       <c r="E18">
         <v>6.4</v>
@@ -753,10 +753,10 @@
         </is>
       </c>
       <c r="C19">
-        <v>0.5005734984007155</v>
+        <v>0.5005734984007153</v>
       </c>
       <c r="D19">
-        <v>0.1924087682127198</v>
+        <v>0.19240876821272</v>
       </c>
       <c r="E19">
         <v>19.2</v>
@@ -774,10 +774,10 @@
         </is>
       </c>
       <c r="C20">
-        <v>0.1632601934381945</v>
+        <v>0.1632601934381949</v>
       </c>
       <c r="D20">
-        <v>0.07300593961981548</v>
+        <v>0.07300593961981573</v>
       </c>
       <c r="E20">
         <v>7.3</v>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="C21">
-        <v>0.742520822665059</v>
+        <v>0.7425208226650581</v>
       </c>
       <c r="D21">
-        <v>0.3320370336720369</v>
+        <v>0.3320370336720366</v>
       </c>
       <c r="E21">
         <v>33.2</v>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="C22">
-        <v>0.3261848029070652</v>
+        <v>0.3261848029070629</v>
       </c>
       <c r="D22">
-        <v>0.1458618143494341</v>
+        <v>0.1458618143494332</v>
       </c>
       <c r="E22">
         <v>14.6</v>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="C23">
-        <v>0.04091434780610793</v>
+        <v>0.04091434780610775</v>
       </c>
       <c r="D23">
-        <v>0.01829588917305573</v>
+        <v>0.01829588917305566</v>
       </c>
       <c r="E23">
         <v>1.8</v>
@@ -858,10 +858,10 @@
         </is>
       </c>
       <c r="C24">
-        <v>0.2864368731575839</v>
+        <v>0.2864368731575846</v>
       </c>
       <c r="D24">
-        <v>0.1280875186182346</v>
+        <v>0.128087518618235</v>
       </c>
       <c r="E24">
         <v>12.8</v>
@@ -879,10 +879,10 @@
         </is>
       </c>
       <c r="C25">
-        <v>-0.0616087293107605</v>
+        <v>-0.06160872931076063</v>
       </c>
       <c r="D25">
-        <v>0.02754990715981036</v>
+        <v>0.02754990715981043</v>
       </c>
       <c r="E25">
         <v>2.8</v>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="C26">
-        <v>0.051085078889516</v>
+        <v>0.05108507888951599</v>
       </c>
       <c r="D26">
-        <v>0.02284398974630274</v>
+        <v>0.02284398974630275</v>
       </c>
       <c r="E26">
         <v>2.3</v>
@@ -921,10 +921,10 @@
         </is>
       </c>
       <c r="C27">
-        <v>-0.4641941522437476</v>
+        <v>-0.4641941522437497</v>
       </c>
       <c r="D27">
-        <v>0.2075761980730951</v>
+        <v>0.2075761980730962</v>
       </c>
       <c r="E27">
         <v>20.8</v>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="C28">
-        <v>-0.1000540531382306</v>
+        <v>-0.1000540531382296</v>
       </c>
       <c r="D28">
-        <v>0.04474170958821483</v>
+        <v>0.0447417095882144</v>
       </c>
       <c r="E28">
         <v>4.5</v>
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="C29">
-        <v>-0.06169281786311936</v>
+        <v>-0.06169281786311794</v>
       </c>
       <c r="D29">
-        <v>0.03100942023226419</v>
+        <v>0.03100942023226356</v>
       </c>
       <c r="E29">
         <v>3.1</v>
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="C30">
-        <v>-0.1221179051587635</v>
+        <v>-0.1221179051587629</v>
       </c>
       <c r="D30">
-        <v>0.06138162544874892</v>
+        <v>0.06138162544874878</v>
       </c>
       <c r="E30">
         <v>6.1</v>
@@ -1005,10 +1005,10 @@
         </is>
       </c>
       <c r="C31">
-        <v>-0.7526860625411183</v>
+        <v>-0.7526860625411215</v>
       </c>
       <c r="D31">
-        <v>0.3783318581442028</v>
+        <v>0.3783318581442056</v>
       </c>
       <c r="E31">
         <v>37.8</v>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="C32">
-        <v>0.01531373451383948</v>
+        <v>0.01531373451383646</v>
       </c>
       <c r="D32">
-        <v>0.007697330828988745</v>
+        <v>0.007697330828987248</v>
       </c>
       <c r="E32">
         <v>0.8</v>
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="C33">
-        <v>0.3864221733685519</v>
+        <v>0.3864221733685499</v>
       </c>
       <c r="D33">
-        <v>0.1942321322983964</v>
+        <v>0.1942321322983959</v>
       </c>
       <c r="E33">
         <v>19.4</v>
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="C34">
-        <v>0.0008935739828158232</v>
+        <v>0.000893573982817546</v>
       </c>
       <c r="D34">
-        <v>0.0004491480872738469</v>
+        <v>0.0004491480872747142</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="C35">
-        <v>0.1177278723958901</v>
+        <v>0.1177278723958896</v>
       </c>
       <c r="D35">
-        <v>0.05917500925755156</v>
+        <v>0.05917500925755147</v>
       </c>
       <c r="E35">
         <v>5.9</v>
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="C36">
-        <v>-0.5002809667327948</v>
+        <v>-0.5002809667327907</v>
       </c>
       <c r="D36">
-        <v>0.2514623787495158</v>
+        <v>0.2514623787495144</v>
       </c>
       <c r="E36">
         <v>25.1</v>
@@ -1131,10 +1131,10 @@
         </is>
       </c>
       <c r="C37">
-        <v>0.03235123020893296</v>
+        <v>0.03235123020893386</v>
       </c>
       <c r="D37">
-        <v>0.01626109695305783</v>
+        <v>0.01626109695305833</v>
       </c>
       <c r="E37">
         <v>1.6</v>
@@ -1152,10 +1152,10 @@
         </is>
       </c>
       <c r="C38">
-        <v>-0.4644964098222302</v>
+        <v>-0.4644964098222303</v>
       </c>
       <c r="D38">
-        <v>0.1791284275046476</v>
+        <v>0.1791284275046478</v>
       </c>
       <c r="E38">
         <v>17.9</v>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="C39">
-        <v>-0.3079170398425684</v>
+        <v>-0.3079170398425702</v>
       </c>
       <c r="D39">
-        <v>0.1187451484716416</v>
+        <v>0.1187451484716424</v>
       </c>
       <c r="E39">
         <v>11.9</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="C40">
-        <v>0.3183728466368139</v>
+        <v>0.3183728466368113</v>
       </c>
       <c r="D40">
-        <v>0.1227773265245622</v>
+        <v>0.1227773265245613</v>
       </c>
       <c r="E40">
         <v>12.3</v>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="C41">
-        <v>0.5426909920221323</v>
+        <v>0.5426909920221321</v>
       </c>
       <c r="D41">
         <v>0.2092833915746865</v>
@@ -1236,10 +1236,10 @@
         </is>
       </c>
       <c r="C42">
-        <v>-0.2072382882995222</v>
+        <v>-0.2072382882995185</v>
       </c>
       <c r="D42">
-        <v>0.07991938778613054</v>
+        <v>0.07991938778612918</v>
       </c>
       <c r="E42">
         <v>8</v>
@@ -1257,10 +1257,10 @@
         </is>
       </c>
       <c r="C43">
-        <v>-0.0375332890545686</v>
+        <v>-0.03753328905456943</v>
       </c>
       <c r="D43">
-        <v>0.01447434017842114</v>
+        <v>0.01447434017842146</v>
       </c>
       <c r="E43">
         <v>1.4</v>
@@ -1278,10 +1278,10 @@
         </is>
       </c>
       <c r="C44">
-        <v>0.1285813095440758</v>
+        <v>0.128581309544076</v>
       </c>
       <c r="D44">
-        <v>0.04958610507653557</v>
+        <v>0.04958610507653569</v>
       </c>
       <c r="E44">
         <v>5</v>
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="C45">
-        <v>-0.4675075683078376</v>
+        <v>-0.4675075683078405</v>
       </c>
       <c r="D45">
-        <v>0.1802896508706163</v>
+        <v>0.1802896508706175</v>
       </c>
       <c r="E45">
         <v>18</v>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="C46">
-        <v>-0.1187537958362092</v>
+        <v>-0.1187537958362082</v>
       </c>
       <c r="D46">
-        <v>0.04579622201275852</v>
+        <v>0.04579622201275817</v>
       </c>
       <c r="E46">
         <v>4.6</v>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="C47">
-        <v>0.1690008497170208</v>
+        <v>0.1690008497170219</v>
       </c>
       <c r="D47">
-        <v>0.06121155127284841</v>
+        <v>0.06121155127284875</v>
       </c>
       <c r="E47">
         <v>6.1</v>
@@ -1365,7 +1365,7 @@
         <v>-0.5048787616089383</v>
       </c>
       <c r="D48">
-        <v>0.1828654249641043</v>
+        <v>0.1828654249641042</v>
       </c>
       <c r="E48">
         <v>18.3</v>
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="C49">
-        <v>0.4406518174906146</v>
+        <v>0.4406518174906119</v>
       </c>
       <c r="D49">
-        <v>0.1596026372942196</v>
+        <v>0.1596026372942186</v>
       </c>
       <c r="E49">
         <v>16</v>
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="C50">
-        <v>-0.3173442865753514</v>
+        <v>-0.3173442865753526</v>
       </c>
       <c r="D50">
-        <v>0.1149410556300666</v>
+        <v>0.114941055630067</v>
       </c>
       <c r="E50">
         <v>11.5</v>
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="C51">
-        <v>0.4872839783381071</v>
+        <v>0.4872839783381088</v>
       </c>
       <c r="D51">
-        <v>0.176492652400413</v>
+        <v>0.1764926524004135</v>
       </c>
       <c r="E51">
         <v>17.6</v>
@@ -1446,10 +1446,10 @@
         </is>
       </c>
       <c r="C52">
-        <v>-0.2111746196562813</v>
+        <v>-0.211174619656281</v>
       </c>
       <c r="D52">
-        <v>0.07648675187289816</v>
+        <v>0.07648675187289801</v>
       </c>
       <c r="E52">
         <v>7.6</v>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="C53">
-        <v>-0.1498109548422406</v>
+        <v>-0.1498109548422413</v>
       </c>
       <c r="D53">
-        <v>0.05426103453867202</v>
+        <v>0.05426103453867225</v>
       </c>
       <c r="E53">
         <v>5.4</v>
@@ -1488,10 +1488,10 @@
         </is>
       </c>
       <c r="C54">
-        <v>-0.2121641209988783</v>
+        <v>-0.212164120998878</v>
       </c>
       <c r="D54">
-        <v>0.0768451460009061</v>
+        <v>0.07684514600090592</v>
       </c>
       <c r="E54">
         <v>7.7</v>
@@ -1509,10 +1509,10 @@
         </is>
       </c>
       <c r="C55">
-        <v>0.2686212881165432</v>
+        <v>0.2686212881165433</v>
       </c>
       <c r="D55">
-        <v>0.09729374602587189</v>
+        <v>0.09729374602587187</v>
       </c>
       <c r="E55">
         <v>9.699999999999999</v>
@@ -1530,10 +1530,10 @@
         </is>
       </c>
       <c r="C56">
-        <v>-0.2473440603924284</v>
+        <v>-0.2473440603924278</v>
       </c>
       <c r="D56">
-        <v>0.1011535609812344</v>
+        <v>0.1011535609812341</v>
       </c>
       <c r="E56">
         <v>10.1</v>
@@ -1554,7 +1554,7 @@
         <v>0.118460113951397</v>
       </c>
       <c r="D57">
-        <v>0.04844532082725289</v>
+        <v>0.04844532082725287</v>
       </c>
       <c r="E57">
         <v>4.8</v>
@@ -1572,10 +1572,10 @@
         </is>
       </c>
       <c r="C58">
-        <v>-0.05471866514157924</v>
+        <v>-0.05471866514158075</v>
       </c>
       <c r="D58">
-        <v>0.02237768646002189</v>
+        <v>0.0223776864600225</v>
       </c>
       <c r="E58">
         <v>2.2</v>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="C59">
-        <v>0.4546884915443258</v>
+        <v>0.4546884915443257</v>
       </c>
       <c r="D59">
-        <v>0.1859489165978872</v>
+        <v>0.1859489165978871</v>
       </c>
       <c r="E59">
         <v>18.6</v>
@@ -1614,10 +1614,10 @@
         </is>
       </c>
       <c r="C60">
-        <v>0.4836008179796511</v>
+        <v>0.4836008179796516</v>
       </c>
       <c r="D60">
-        <v>0.197772870528881</v>
+        <v>0.1977728705288812</v>
       </c>
       <c r="E60">
         <v>19.8</v>
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="C61">
-        <v>-0.5168495930526169</v>
+        <v>-0.5168495930526167</v>
       </c>
       <c r="D61">
-        <v>0.2113702538319553</v>
+        <v>0.2113702538319551</v>
       </c>
       <c r="E61">
         <v>21.1</v>
@@ -1656,10 +1656,10 @@
         </is>
       </c>
       <c r="C62">
-        <v>-0.07779777290877467</v>
+        <v>-0.07779777290877499</v>
       </c>
       <c r="D62">
-        <v>0.0318160935566693</v>
+        <v>0.03181609355666942</v>
       </c>
       <c r="E62">
         <v>3.2</v>
@@ -1677,10 +1677,10 @@
         </is>
       </c>
       <c r="C63">
-        <v>0.4545443664017518</v>
+        <v>0.4545443664017513</v>
       </c>
       <c r="D63">
-        <v>0.1858899753345508</v>
+        <v>0.1858899753345505</v>
       </c>
       <c r="E63">
         <v>18.6</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="C64">
-        <v>0.03722946477052047</v>
+        <v>0.03722946477052083</v>
       </c>
       <c r="D64">
-        <v>0.01522532188154715</v>
+        <v>0.01522532188154729</v>
       </c>
       <c r="E64">
         <v>1.5</v>
@@ -1719,10 +1719,10 @@
         </is>
       </c>
       <c r="C65">
-        <v>0.577673296628779</v>
+        <v>0.5776732966287782</v>
       </c>
       <c r="D65">
-        <v>0.2791574522934318</v>
+        <v>0.2791574522934317</v>
       </c>
       <c r="E65">
         <v>27.9</v>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="C66">
-        <v>-0.2593453676096286</v>
+        <v>-0.2593453676096285</v>
       </c>
       <c r="D66">
-        <v>0.1253272264937867</v>
+        <v>0.1253272264937868</v>
       </c>
       <c r="E66">
         <v>12.5</v>
@@ -1761,10 +1761,10 @@
         </is>
       </c>
       <c r="C67">
-        <v>0.0008334875041646162</v>
+        <v>0.0008334875041642667</v>
       </c>
       <c r="D67">
-        <v>0.0004027782650485316</v>
+        <v>0.0004027782650483632</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="C68">
-        <v>0.2375641789926018</v>
+        <v>0.2375641789926016</v>
       </c>
       <c r="D68">
-        <v>0.1148015865555445</v>
+        <v>0.1148015865555446</v>
       </c>
       <c r="E68">
         <v>11.5</v>
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="C69">
-        <v>0.09361934975388878</v>
+        <v>0.09361934975388894</v>
       </c>
       <c r="D69">
-        <v>0.04524103730461636</v>
+        <v>0.0452410373046165</v>
       </c>
       <c r="E69">
         <v>4.5</v>
@@ -1824,10 +1824,10 @@
         </is>
       </c>
       <c r="C70">
-        <v>-0.06681677474309178</v>
+        <v>-0.06681677474309126</v>
       </c>
       <c r="D70">
-        <v>0.03228883993184112</v>
+        <v>0.03228883993184091</v>
       </c>
       <c r="E70">
         <v>3.2</v>
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="C71">
-        <v>0.07035711622674458</v>
+        <v>0.07035711622674473</v>
       </c>
       <c r="D71">
-        <v>0.03399969053648724</v>
+        <v>0.03399969053648735</v>
       </c>
       <c r="E71">
         <v>3.4</v>
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="C72">
-        <v>0.04007983170517476</v>
+        <v>0.0400798317051743</v>
       </c>
       <c r="D72">
-        <v>0.01936835884999551</v>
+        <v>0.01936835884999532</v>
       </c>
       <c r="E72">
         <v>1.9</v>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="C73">
-        <v>-0.7230563795935622</v>
+        <v>-0.7230563795935619</v>
       </c>
       <c r="D73">
-        <v>0.3494130297692482</v>
+        <v>0.3494130297692485</v>
       </c>
       <c r="E73">
         <v>34.9</v>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="C74">
-        <v>7.113096148388175E-17</v>
+        <v>-5.169090912457923E-18</v>
       </c>
       <c r="D74">
-        <v>3.922079511226853E-17</v>
+        <v>2.850177354064605E-18</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -1929,10 +1929,10 @@
         </is>
       </c>
       <c r="C75">
-        <v>-2.06467072481531E-16</v>
+        <v>5.038391791941544E-17</v>
       </c>
       <c r="D75">
-        <v>1.138435721702283E-16</v>
+        <v>2.778111360294956E-17</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -1950,10 +1950,10 @@
         </is>
       </c>
       <c r="C76">
-        <v>1.377356125383819E-16</v>
+        <v>8.427467616089917E-17</v>
       </c>
       <c r="D76">
-        <v>7.594583464550514E-17</v>
+        <v>4.646808840912957E-17</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="C77">
-        <v>0.2950591148318302</v>
+        <v>0.2950591148318303</v>
       </c>
       <c r="D77">
-        <v>0.1626922067045142</v>
+        <v>0.1626922067045143</v>
       </c>
       <c r="E77">
         <v>16.3</v>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="C78">
-        <v>0.2118052329527123</v>
+        <v>0.2118052329527117</v>
       </c>
       <c r="D78">
-        <v>0.1167869725369456</v>
+        <v>0.1167869725369453</v>
       </c>
       <c r="E78">
         <v>11.7</v>
@@ -2013,10 +2013,10 @@
         </is>
       </c>
       <c r="C79">
-        <v>0.5688254307957967</v>
+        <v>0.5688254307957972</v>
       </c>
       <c r="D79">
-        <v>0.3136438086942662</v>
+        <v>0.3136438086942665</v>
       </c>
       <c r="E79">
         <v>31.4</v>
@@ -2034,10 +2034,10 @@
         </is>
       </c>
       <c r="C80">
-        <v>-0.7379134714371871</v>
+        <v>-0.7379134714371872</v>
       </c>
       <c r="D80">
-        <v>0.4068770120642735</v>
+        <v>0.4068770120642736</v>
       </c>
       <c r="E80">
         <v>40.7</v>
@@ -2055,10 +2055,10 @@
         </is>
       </c>
       <c r="C81">
-        <v>2.125338778830952E-16</v>
+        <v>4.300012994629781E-16</v>
       </c>
       <c r="D81">
-        <v>1.171887389819362E-16</v>
+        <v>2.370977772888433E-16</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="C82">
-        <v>-1.852673959730948E-16</v>
+        <v>-5.763313016793662E-17</v>
       </c>
       <c r="D82">
-        <v>1.021543140547991E-16</v>
+        <v>3.177824596828421E-17</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.2796110343189929</v>
+        <v>0.279611034318993</v>
       </c>
     </row>
     <row r="3">
@@ -2124,7 +2124,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.1877147371539325</v>
+        <v>0.1877147371539326</v>
       </c>
     </row>
     <row r="4">
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.1345284542145642</v>
+        <v>0.1345284542145638</v>
       </c>
     </row>
     <row r="5">
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.1117926908085879</v>
+        <v>0.1117926908085881</v>
       </c>
     </row>
     <row r="6">
@@ -2174,7 +2174,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.06319928565342506</v>
+        <v>0.06319928565342511</v>
       </c>
     </row>
     <row r="9">
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.03680238909606984</v>
+        <v>0.03680238909606981</v>
       </c>
     </row>
     <row r="10">
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>6.014579218727985E-31</v>
+        <v>5.594841483977168E-31</v>
       </c>
     </row>
   </sheetData>
@@ -2231,7 +2231,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.5904655784019618</v>
+        <v>0.5904655784019622</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.5003681093865645</v>
+        <v>0.5003681093865647</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.357648340525302</v>
+        <v>0.3576483405253019</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.3254249083447185</v>
+        <v>0.3254249083447182</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.2600068618528435</v>
+        <v>0.2600068618528437</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.2213110964443284</v>
+        <v>0.2213110964443281</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.1863165917715679</v>
+        <v>0.1863165917715682</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.1148517480293739</v>
+        <v>0.1148517480293745</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>-0.05178304128717547</v>
+        <v>-0.05178304128717581</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.5005734984007155</v>
+        <v>0.5005734984007153</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.3830548014776221</v>
+        <v>0.3830548014776216</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>-0.3648822813276321</v>
+        <v>-0.3648822813276324</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>-0.3235297503896482</v>
+        <v>-0.3235297503896475</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>-0.200961388186444</v>
+        <v>-0.2009613881864435</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>-0.1665381529164315</v>
+        <v>-0.1665381529164311</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>-0.1238794609034083</v>
+        <v>-0.1238794609034084</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.007763770756149372</v>
+        <v>0.007763770756148314</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
